--- a/validation/expert_reviews/E5_extraction_review.xlsx
+++ b/validation/expert_reviews/E5_extraction_review.xlsx
@@ -578,7 +578,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Review workbook — James</t>
+          <t>Review workbook — E5</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: James    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E5    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — James</t>
+          <t>Rating — E5</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: James    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E5    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — James</t>
+          <t>Rating — E5</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: James    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E5    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — James</t>
+          <t>Rating — E5</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: James    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E5    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — James</t>
+          <t>Rating — E5</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2909,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: James    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E5    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -2969,6 +2969,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -3084,6 +3085,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -3426,7 +3428,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: James    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E5    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -3486,6 +3488,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -3601,6 +3604,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -3943,7 +3947,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: James    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E5    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4003,6 +4007,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4118,6 +4123,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -4460,7 +4466,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: James    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E5    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -4520,6 +4526,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -4635,6 +4642,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -4977,7 +4985,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: James    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E5    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5037,6 +5045,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5152,6 +5161,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -5494,7 +5504,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Grader: James    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
+          <t>Grader: E5    —    Read the paper and extract entities below. See the separate prompt document for entity definitions and the full extraction guidelines.</t>
         </is>
       </c>
     </row>
@@ -5554,6 +5564,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
@@ -5669,6 +5680,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
@@ -6016,7 +6028,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: James    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E5    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -6035,7 +6047,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — James</t>
+          <t>Rating — E5</t>
         </is>
       </c>
     </row>
@@ -6543,7 +6555,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Grader: James    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
+          <t>Grader: E5    —    For each entity (extracted by the model), choose ONE rating (type 'x'). Add notes if helpful. Compare to your own from-scratch [ENTRY] sheet.</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6574,7 @@
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>Rating — James</t>
+          <t>Rating — E5</t>
         </is>
       </c>
     </row>
